--- a/reports/gpt-oss-20b-exj.xlsx
+++ b/reports/gpt-oss-20b-exj.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-10 11:32:10</t>
+          <t>2026-02-24 21:14:13</t>
         </is>
       </c>
     </row>
